--- a/liaisons_Super_Constellation/Reseau_TWA_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_TWA_L1049_sourced.xlsx
@@ -1012,6 +1012,33 @@
       <c r="A20" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
       </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1444,6 +1471,33 @@
       <c r="A14" t="str">
         <v>[R] Vols retour ajoutés automatiquement (itinéraire miroir, horaires reconstitués).</v>
       </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
